--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104640_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104640_W21.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2075</v>
+        <v>2.4654</v>
       </c>
       <c r="E2" t="n">
-        <v>1.749</v>
+        <v>2.1215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4584</v>
+        <v>0.3439</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.7994</v>
+        <v>-2.8017</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.101</v>
+        <v>-2.0968</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6984</v>
+        <v>-0.7049</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.686</v>
+        <v>-2.7211</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1398</v>
+        <v>-1.1484</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.5462</v>
+        <v>-1.5727</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1134</v>
+        <v>-0.0806</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8478</v>
+        <v>0.8678</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7002</v>
+        <v>-0.4354</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2571</v>
+        <v>0.1691</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4431</v>
+        <v>-0.6045</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W2" t="n">
-        <v>4.6921</v>
+        <v>4.6734</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9621</v>
+        <v>1.8169</v>
       </c>
       <c r="E3" t="n">
-        <v>3.973</v>
+        <v>3.3423</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0109</v>
+        <v>-1.5255</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2486</v>
+        <v>-0.2537</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.277</v>
+        <v>-2.2748</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0284</v>
+        <v>2.0211</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9389</v>
+        <v>0.9048</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4413</v>
+        <v>-1.4554</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3802</v>
+        <v>2.3602</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1875</v>
+        <v>-1.1585</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8357</v>
+        <v>-0.8194</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2619</v>
+        <v>0.1114</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5293</v>
+        <v>-0.0585</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2674</v>
+        <v>0.1699</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X3" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9327</v>
+        <v>0.6361</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3195</v>
+        <v>0.7165</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3868</v>
+        <v>-0.0803</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1906</v>
+        <v>2.1865</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1658</v>
+        <v>-0.1747</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3564</v>
+        <v>2.3613</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6377</v>
+        <v>2.6123</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4014</v>
+        <v>0.3857</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2363</v>
+        <v>2.2265</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4471</v>
+        <v>-0.4257</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1201</v>
+        <v>0.1347</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1031</v>
+        <v>-0.1846</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0162</v>
+        <v>0.4504</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9131</v>
+        <v>-0.635</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.5504</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2275</v>
+        <v>2.208</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5729</v>
+        <v>-1.6577</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0449</v>
+        <v>-1.0363</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3867</v>
+        <v>-0.3904</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6583</v>
+        <v>-0.6459</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6253</v>
+        <v>0.6091</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4014</v>
+        <v>0.3857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6702</v>
+        <v>-1.6455</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8822</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1948</v>
+        <v>0.0907</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0484</v>
+        <v>-0.0258</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2431</v>
+        <v>0.1165</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>4.1458</v>
+        <v>4.1287</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9604</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4727</v>
+        <v>0.4879</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4643</v>
+        <v>1.6092</v>
       </c>
       <c r="F6" t="n">
-        <v>1.937</v>
+        <v>-1.1213</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3835</v>
+        <v>3.4251</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.019</v>
+        <v>1.3617</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4025</v>
+        <v>2.0634</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0482</v>
+        <v>4.2247</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0217</v>
+        <v>1.8788</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0265</v>
+        <v>2.3459</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6647</v>
+        <v>-0.7997</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0407</v>
+        <v>-0.5171</v>
       </c>
       <c r="O6" t="n">
-        <v>0.376</v>
+        <v>-0.2826</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8562</v>
+        <v>-2.5039</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9488</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6109</v>
+        <v>-0.4819</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2511</v>
+        <v>-0.1116</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3599</v>
+        <v>-0.3703</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7071</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. RICE</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2587</v>
+        <v>0.3194</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4731</v>
+        <v>-1.669</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2144</v>
+        <v>1.9883</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2097</v>
+        <v>0.3969</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0204</v>
+        <v>-0.0037</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1893</v>
+        <v>0.4006</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7581</v>
+        <v>1.0235</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9426</v>
+        <v>1.017</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8156</v>
+        <v>0.0066</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5485</v>
+        <v>-0.6266</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07779999999999999</v>
+        <v>-1.0207</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6263</v>
+        <v>0.3941</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1793</v>
+        <v>0.446</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2571</v>
+        <v>0.0877</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4364</v>
+        <v>0.3583</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9961</v>
+        <v>0.387</v>
       </c>
       <c r="W7" t="n">
-        <v>2.8282</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.8243</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>R. GUERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0301</v>
+        <v>0.0465</v>
       </c>
       <c r="E8" t="n">
-        <v>1.326</v>
+        <v>1.6908</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2959</v>
+        <v>-1.6444</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4259</v>
+        <v>0.6738</v>
       </c>
       <c r="H8" t="n">
-        <v>1.368</v>
+        <v>0.5544</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0578</v>
+        <v>0.1194</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2385</v>
+        <v>0.6433</v>
       </c>
       <c r="K8" t="n">
-        <v>1.8875</v>
+        <v>0.5688</v>
       </c>
       <c r="L8" t="n">
-        <v>2.351</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8126</v>
+        <v>0.0305</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5195</v>
+        <v>-0.0144</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2931</v>
+        <v>0.0449</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9421</v>
+        <v>0.0964</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.0419</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5247000000000001</v>
+        <v>0.1383</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GUERRERO</t>
+          <t>S. RICE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>-0.0313</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4605</v>
+        <v>1.5474</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6306</v>
+        <v>-1.5787</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6702</v>
+        <v>2.1994</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5556</v>
+        <v>2.0055</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1147</v>
+        <v>0.1939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6461</v>
+        <v>2.7237</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5715</v>
+        <v>1.9198</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0746</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0241</v>
+        <v>-0.5243</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0159</v>
+        <v>0.0857</v>
       </c>
       <c r="O9" t="n">
-        <v>0.04</v>
+        <v>-0.61</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.8697</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>2.7316</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1086</v>
+        <v>-0.0893</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2782</v>
+        <v>-0.1165</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1697</v>
+        <v>0.0272</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.639</v>
+        <v>-1.0032</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>2.81</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7317</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>R. LUZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7548</v>
+        <v>-0.7022</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1451</v>
+        <v>-0.0332</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3903</v>
+        <v>-0.669</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9586</v>
+        <v>2.6262</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2655</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6929999999999999</v>
+        <v>2.7157</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5705</v>
+        <v>4.6033</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6825</v>
+        <v>1.7064</v>
       </c>
       <c r="L10" t="n">
-        <v>0.112</v>
+        <v>2.8968</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.388</v>
+        <v>-1.977</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5831</v>
+        <v>-1.7959</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.805</v>
+        <v>-0.1811</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0696</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3478</v>
+        <v>-0.0838</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4174</v>
+        <v>0.1699</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. LUZ</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3035</v>
+        <v>-0.7428</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5403</v>
+        <v>-1.1507</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7632</v>
+        <v>0.4079</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6167</v>
+        <v>-1.9506</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0968</v>
+        <v>-1.2611</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7135</v>
+        <v>-0.6895</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6224</v>
+        <v>-0.5745</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7144</v>
+        <v>-0.6862</v>
       </c>
       <c r="L11" t="n">
-        <v>2.908</v>
+        <v>0.1117</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0056</v>
+        <v>-1.3761</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8112</v>
+        <v>-0.5749</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1945</v>
+        <v>-0.8012</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.4025</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5178</v>
+        <v>0.0697</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6261</v>
+        <v>-0.3485</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1083</v>
+        <v>0.4182</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.568</v>
+        <v>-1.4145</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3176</v>
+        <v>1.6554</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8857</v>
+        <v>-3.0699</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7664</v>
+        <v>1.7795</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1502</v>
+        <v>-0.1439</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9166</v>
+        <v>1.9234</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9122</v>
+        <v>1.9066</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6061</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1458</v>
+        <v>-0.1271</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3759</v>
+        <v>-0.2426</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U12" t="n">
-        <v>0.111</v>
+        <v>-0.11</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.9851</v>
+        <v>-3.9709</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.722199999999999</v>
+        <v>3.431799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>11.6965</v>
+        <v>12.0382</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.9747</v>
+        <v>-8.606700000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2115</v>
+        <v>7.245100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.518000000000001</v>
+        <v>-2.513200000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>9.7295</v>
+        <v>9.7585</v>
       </c>
       <c r="J13" t="n">
-        <v>16.1709</v>
+        <v>15.9557</v>
       </c>
       <c r="K13" t="n">
-        <v>5.282999999999999</v>
+        <v>5.175499999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>10.888</v>
+        <v>10.7801</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.959299999999999</v>
+        <v>-8.710600000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.800999999999998</v>
+        <v>-7.688899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1584</v>
+        <v>-1.0218</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.268299999999999</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.5493</v>
+        <v>-21.6247</v>
       </c>
       <c r="R13" t="n">
-        <v>19.2809</v>
+        <v>19.3489</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.225</v>
+        <v>-0.5336000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9224</v>
+        <v>-0.212</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3025000000000002</v>
+        <v>-0.3215000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9962</v>
+        <v>-1.003200000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>17.9973</v>
+        <v>17.9198</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.9934</v>
+        <v>-18.9229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.564</v>
+        <v>7.7439</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2706</v>
+        <v>7.9462</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2935</v>
+        <v>-0.2022</v>
       </c>
       <c r="G14" t="n">
-        <v>1.5804</v>
+        <v>3.2408</v>
       </c>
       <c r="H14" t="n">
-        <v>0.746</v>
+        <v>-0.6601</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8344</v>
+        <v>3.9009</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5312</v>
+        <v>5.144</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1878</v>
+        <v>0.4752</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3434</v>
+        <v>4.6688</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9507</v>
+        <v>-1.9032</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4417</v>
+        <v>-1.1353</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.509</v>
+        <v>-0.768</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>3.1868</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4768</v>
+        <v>0.5424</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3157</v>
+        <v>0.0785</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1612</v>
+        <v>0.4639</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5994</v>
+        <v>0.7739</v>
       </c>
       <c r="W14" t="n">
-        <v>4.6921</v>
+        <v>2.7237</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.9497</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.5556</v>
+        <v>6.8379</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5275</v>
+        <v>5.2888</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0281</v>
+        <v>1.5491</v>
       </c>
       <c r="G15" t="n">
-        <v>3.2582</v>
+        <v>1.5875</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6521</v>
+        <v>0.744</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9103</v>
+        <v>0.8435</v>
       </c>
       <c r="J15" t="n">
-        <v>5.192</v>
+        <v>2.5159</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4982</v>
+        <v>1.1754</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6938</v>
+        <v>1.3405</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9338</v>
+        <v>-0.9284</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1503</v>
+        <v>-0.4314</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7835</v>
+        <v>-0.497</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1757</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3505</v>
+        <v>0.7559</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3962</v>
+        <v>0.3758</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7467</v>
+        <v>0.3801</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7712</v>
+        <v>3.584</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7317</v>
+        <v>4.6734</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.9604</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.0257</v>
+        <v>4.9561</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9102</v>
+        <v>3.1147</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1155</v>
+        <v>1.8414</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.7214</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5858</v>
+        <v>1.5881</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8716</v>
+        <v>-0.8667</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8858</v>
+        <v>1.8655</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5629</v>
+        <v>2.5511</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6771</v>
+        <v>-0.6856</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1716</v>
+        <v>-1.1441</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5383</v>
+        <v>0.4623</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1875</v>
+        <v>0.0507</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7258</v>
+        <v>0.4116</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. WRIGHT-FOREMAN</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3065</v>
+        <v>0.823</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6441</v>
+        <v>1.8697</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3376</v>
+        <v>-1.0467</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8597</v>
+        <v>-1.5751</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1791</v>
+        <v>-0.2758</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.0388</v>
+        <v>-1.2994</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0105</v>
+        <v>1.0744</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4794</v>
+        <v>0.6583</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4689</v>
+        <v>0.4162</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8702</v>
+        <v>-2.6496</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3003</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5699</v>
+        <v>-1.7155</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.7316</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0457</v>
+        <v>0.1509</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5293</v>
+        <v>0.1901</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.575</v>
+        <v>-0.0392</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3461</v>
+        <v>1.792</v>
       </c>
       <c r="W17" t="n">
-        <v>2.5068</v>
+        <v>2.8814</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>J. WRIGHT-FOREMAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2869</v>
+        <v>0.3804</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6809</v>
+        <v>0.3404</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.394</v>
+        <v>0.04</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5673</v>
+        <v>-0.8819</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2771</v>
+        <v>2.1663</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2902</v>
+        <v>-3.0482</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1052</v>
+        <v>0.9636</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6682</v>
+        <v>2.4541</v>
       </c>
       <c r="L18" t="n">
-        <v>0.437</v>
+        <v>-1.4906</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6725</v>
+        <v>-1.8455</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9453</v>
+        <v>-0.2879</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.7272</v>
+        <v>-1.5576</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R18" t="n">
-        <v>2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3992</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0484</v>
+        <v>0.2968</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3508</v>
+        <v>-0.2331</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7997</v>
+        <v>2.3367</v>
       </c>
       <c r="W18" t="n">
-        <v>2.8924</v>
+        <v>2.4945</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7597</v>
+        <v>-1.0323</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4223</v>
+        <v>-1.309</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6626</v>
+        <v>0.2767</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4202</v>
+        <v>0.4319</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0463</v>
+        <v>-0.0405</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4665</v>
+        <v>0.4725</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1293</v>
+        <v>0.1289</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>0.291</v>
+        <v>0.303</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0735</v>
+        <v>-0.217</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4908</v>
+        <v>0.0827</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1521</v>
+        <v>-1.5927</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4769</v>
+        <v>-1.9557</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3248</v>
+        <v>0.363</v>
       </c>
       <c r="G20" t="n">
-        <v>0.016</v>
+        <v>0.018</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1413</v>
+        <v>-0.14</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5804</v>
+        <v>0.1405</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7168</v>
+        <v>0.2462</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1103</v>
+        <v>-2.483</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0971</v>
+        <v>-1.5755</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0131</v>
+        <v>-0.9075</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9724</v>
+        <v>-1.9729</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3679</v>
+        <v>0.3704</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3404</v>
+        <v>-2.3433</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4661</v>
+        <v>-1.4731</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5063</v>
+        <v>-0.4998</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2986</v>
+        <v>0.3014</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2743</v>
+        <v>-0.1035</v>
       </c>
       <c r="T21" t="n">
-        <v>0.369</v>
+        <v>-0.1024</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.0011</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2448</v>
+        <v>-4.0299</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4038</v>
+        <v>-0.1907</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.841</v>
+        <v>-3.8392</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.1974</v>
+        <v>-3.1949</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4704</v>
+        <v>0.471</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.6678</v>
+        <v>-3.6659</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3835</v>
+        <v>-0.4018</v>
       </c>
       <c r="K22" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3115</v>
+        <v>-1.3186</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8139</v>
+        <v>-2.7931</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.3563</v>
+        <v>-2.3472</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2477</v>
+        <v>-0.043</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0212</v>
+        <v>0.2598</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2689</v>
+        <v>-0.3028</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>I. WASHINGTON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8536</v>
+        <v>-4.5477</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9612</v>
+        <v>-0.8877</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8924</v>
+        <v>-3.66</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7381</v>
+        <v>-2.8511</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8715000000000001</v>
+        <v>-2.4211</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.6096</v>
+        <v>-0.43</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7523</v>
+        <v>-0.5739</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9351</v>
+        <v>-1.645</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6874</v>
+        <v>1.0711</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9858</v>
+        <v>-2.2772</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0636</v>
+        <v>-0.7761</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9222</v>
+        <v>-1.5011</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5692</v>
+        <v>0.1149</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>-0.2652</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>0.3801</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-2.4945</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-3.584</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. WASHINGTON</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0911</v>
+        <v>-4.6748</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5439</v>
+        <v>-2.8689</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.5473</v>
+        <v>-1.8059</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8278</v>
+        <v>-1.7399</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.4198</v>
+        <v>0.873</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.408</v>
+        <v>-2.6129</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5285</v>
+        <v>-0.7679</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6318</v>
+        <v>0.9308</v>
       </c>
       <c r="L24" t="n">
-        <v>1.1033</v>
+        <v>-1.6987</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2993</v>
+        <v>-0.972</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.788</v>
+        <v>-0.0578</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5113</v>
+        <v>-0.9143</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.437</v>
+        <v>-0.3902</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9739</v>
+        <v>-0.3695</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5368000000000001</v>
+        <v>-0.0207</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5068</v>
+        <v>-1.6342</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.5994</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2492</v>
+        <v>-5.1155</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2462</v>
+        <v>-2.2551</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0029</v>
+        <v>-2.8604</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0378</v>
+        <v>-1.0286</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4647</v>
+        <v>-0.4598</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1612</v>
+        <v>0.1607</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.199</v>
+        <v>-1.1893</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3702</v>
+        <v>-0.2462</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2311</v>
+        <v>-0.1067</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.7221</v>
+        <v>-2.734599999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>7.881899999999998</v>
+        <v>7.517199999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-10.6038</v>
+        <v>-10.2517</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.2115</v>
+        <v>-7.244800000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>2.518</v>
+        <v>2.5134</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.7296</v>
+        <v>-9.7583</v>
       </c>
       <c r="J26" t="n">
-        <v>8.959400000000002</v>
+        <v>8.710800000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>7.801000000000001</v>
+        <v>7.689</v>
       </c>
       <c r="L26" t="n">
-        <v>1.1584</v>
+        <v>1.021799999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-16.1707</v>
+        <v>-15.9557</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.282900000000001</v>
+        <v>-5.1757</v>
       </c>
       <c r="O26" t="n">
-        <v>-10.8879</v>
+        <v>-10.7799</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2684</v>
+        <v>2.276299999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-19.2808</v>
+        <v>-19.3488</v>
       </c>
       <c r="R26" t="n">
-        <v>21.5492</v>
+        <v>21.625</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2248</v>
+        <v>1.2307</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3026</v>
+        <v>0.3216000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.9221</v>
+        <v>0.9090999999999998</v>
       </c>
       <c r="V26" t="n">
-        <v>0.996</v>
+        <v>1.003100000000001</v>
       </c>
       <c r="W26" t="n">
-        <v>17.9008</v>
+        <v>17.8334</v>
       </c>
       <c r="X26" t="n">
-        <v>-16.9045</v>
+        <v>-16.8304</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104640_W21.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104640_W21.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.9709</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-18.9229</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.9497</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-3.584</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104640_W21.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-16.8304</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
